--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_07-07-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_07-07-2025.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£12.12</t>
+          <t>£12.44</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£13.15</t>
+          <t>£13.68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£15.55</t>
+          <t>£16.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£17.88</t>
+          <t>£18.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£24.48</t>
+          <t>£23.00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>£25.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£25.60</t>
+          <t>£25.48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£27.62</t>
+          <t>£28.88</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£28.50</t>
+          <t>£31.62</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£37.14</t>
+          <t>£40.00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£36.88</t>
+          <t>£38.82</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£46.88</t>
+          <t>£51.88</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£42.48</t>
+          <t>£48.00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
